--- a/src/data/opportunities_template.xlsx
+++ b/src/data/opportunities_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
   <si>
     <t>Field</t>
   </si>
@@ -113,6 +113,9 @@
     <t>Program</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Portal is a multi-day immersive experience designed to give students a real insight into how Jane Street approaches trading, research, and technology. Selected participants will take part in strategic games, hands-on technical sessions, and talks led by industry professionals.</t>
   </si>
   <si>
@@ -120,9 +123,6 @@
   </si>
   <si>
     <t>Women in Trading Program</t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Jane Street's Women in Trading program is a unique opportunity for women interested in quantitative trading, programming, and mathematics. This cohort's applications are now closed — stay tuned for future rounds.</t>
@@ -174,7 +174,10 @@
 Transaction Services and Group Treasury.</t>
   </si>
   <si>
-    <t>https://au.gradconnection.com/employers/westpac/jobs</t>
+    <t>https://www.westpac.com.au/about-westpac/careers/graduate-program/?fbclid=IwY2xjawTCxK5leHRuA2FlbQIxMQBzcnRjBmFwcF9pZAEwAAEeBHk5ER-QAELI08P6WTO2mM49f9QouUDkJvEyRmNXWUuZDuBQxn_FzR6Y9Ck_aem_e09kyAHItsvhi9qp9stEQQ</t>
+  </si>
+  <si>
+    <t>Westpac Internship Program</t>
   </si>
 </sst>
 </file>
@@ -752,18 +755,18 @@
         <v>46089.0</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>30</v>
@@ -781,7 +784,7 @@
         <v>46068.0</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>37</v>
@@ -810,7 +813,7 @@
         <v>46142.0</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>40</v>
@@ -836,7 +839,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>44</v>
@@ -862,7 +865,7 @@
         <v>49</v>
       </c>
       <c r="F6" s="18">
-        <v>46122.0</v>
+        <v>46248.0</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>22</v>
@@ -874,11 +877,34 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" s="11"/>
-      <c r="F7" s="18"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="5"/>
+    <row r="7" ht="127.5" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="18">
+        <v>46234.0</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -887,7 +913,8 @@
     <hyperlink r:id="rId3" ref="I4"/>
     <hyperlink r:id="rId4" ref="I5"/>
     <hyperlink r:id="rId5" ref="I6"/>
+    <hyperlink r:id="rId6" ref="I7"/>
   </hyperlinks>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>